--- a/internal_doc/05.测试设计/驱动测试/PHP 驱动/PHP驱动_接口分析.xlsx
+++ b/internal_doc/05.测试设计/驱动测试/PHP 驱动/PHP驱动_接口分析.xlsx
@@ -22,12 +22,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SequoiaGroup &amp; Node'!$A$1:$G$44</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="331">
   <si>
     <t>备注</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -229,18 +228,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>createCataGroup</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>removeGroup (string $name)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>removeGroup</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>execSQL (string $sql)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -317,10 +308,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Eval javascript code</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>事务</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -358,14 +345,6 @@
   </si>
   <si>
     <t>removeProcedure</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>evalJs (string $code)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>evalJs</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1617,10 +1596,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>createGroup</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Judge whether the specified replica group is catalog</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1712,12 +1687,32 @@
     <t xml:space="preserve">__construct </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>createGroup</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeGroup</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>createCataGroup</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>evalJs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>evalJs (string $code)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1765,13 +1760,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -1781,7 +1769,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1795,17 +1783,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1813,32 +1796,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1862,9 +1827,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1874,14 +1836,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="Neutral" xfId="1" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="2" builtinId="10"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2187,7 +2148,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="40.5">
       <c r="A1" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -2200,7 +2161,7 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2227,47 +2188,46 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="27">
-      <c r="A2" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>331</v>
+      <c r="A2" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>325</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
+      <c r="B3" s="12"/>
     </row>
     <row r="4" spans="1:7" ht="27">
-      <c r="A4" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" s="13" t="s">
+      <c r="A4" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -2276,7 +2236,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
@@ -2287,7 +2247,7 @@
     </row>
     <row r="8" spans="1:7" ht="27">
       <c r="A8" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>9</v>
@@ -2298,7 +2258,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>11</v>
@@ -2309,7 +2269,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>13</v>
@@ -2320,7 +2280,7 @@
     </row>
     <row r="14" spans="1:7" ht="42.75" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>15</v>
@@ -2329,12 +2289,12 @@
         <v>14</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>18</v>
@@ -2345,7 +2305,7 @@
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="43.5" customHeight="1">
       <c r="A18" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>20</v>
@@ -2354,37 +2314,37 @@
         <v>19</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="40.5">
       <c r="A20" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="27">
       <c r="A22" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>25</v>
@@ -2395,7 +2355,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>27</v>
@@ -2406,7 +2366,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>29</v>
@@ -2417,7 +2377,7 @@
     </row>
     <row r="30" spans="1:5" ht="40.5">
       <c r="A30" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>31</v>
@@ -2428,7 +2388,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>33</v>
@@ -2439,7 +2399,7 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="5" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>35</v>
@@ -2450,7 +2410,7 @@
     </row>
     <row r="36" spans="1:3" ht="40.5">
       <c r="A36" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>37</v>
@@ -2464,7 +2424,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>39</v>
@@ -2478,7 +2438,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>41</v>
@@ -2492,7 +2452,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>43</v>
@@ -2506,7 +2466,7 @@
     </row>
     <row r="44" spans="1:3" ht="40.5">
       <c r="A44" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>45</v>
@@ -2517,7 +2477,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>47</v>
@@ -2528,10 +2488,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>311</v>
+        <v>62</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>326</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>48</v>
@@ -2539,389 +2499,386 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>52</v>
+        <v>327</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="27">
       <c r="A52" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>50</v>
+        <v>62</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>328</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="40.5">
       <c r="A64" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" ht="40.5">
-      <c r="A70" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>84</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>329</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="13"/>
+        <v>330</v>
+      </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="40.5">
       <c r="A80" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="40.5">
       <c r="A84" s="5" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="27">
       <c r="A88" s="5" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="27" hidden="1">
       <c r="A94" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="27" hidden="1">
       <c r="A96" s="5" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="27" hidden="1">
       <c r="A98" s="5" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="27" hidden="1">
       <c r="A100" s="5" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="27" hidden="1">
       <c r="A102" s="5" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="27" hidden="1">
       <c r="A104" s="5" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="27" hidden="1">
       <c r="A106" s="5" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="27" hidden="1">
       <c r="A108" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -2945,7 +2902,7 @@
     <col min="1" max="1" width="10" style="5" customWidth="1"/>
     <col min="2" max="2" width="16" style="1" customWidth="1"/>
     <col min="3" max="3" width="55.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="11" customWidth="1"/>
+    <col min="4" max="4" width="13" style="10" customWidth="1"/>
     <col min="5" max="5" width="41.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.25" style="3" customWidth="1"/>
     <col min="7" max="7" width="41.125" style="1" customWidth="1"/>
@@ -2954,39 +2911,39 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>294</v>
+      <c r="D1" s="9" t="s">
+        <v>289</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="27">
       <c r="A2" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -2996,13 +2953,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -3012,234 +2969,234 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="27">
       <c r="A22" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="27">
       <c r="A24" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="27">
       <c r="A26" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="27">
       <c r="A28" s="5" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="5" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="5" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>220</v>
-      </c>
       <c r="C34" s="1" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>241</v>
+        <v>313</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -3267,117 +3224,117 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="27">
       <c r="A4" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -3387,32 +3344,32 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="40.5">
       <c r="A18" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="40.5">
       <c r="A20" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>31</v>
@@ -3421,12 +3378,12 @@
         <v>30</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="40.5">
       <c r="A22" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>45</v>
@@ -3435,7 +3392,7 @@
         <v>44</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -3481,7 +3438,7 @@
     <col min="1" max="1" width="12.75" style="5" customWidth="1"/>
     <col min="2" max="2" width="21.625" style="1" customWidth="1"/>
     <col min="3" max="3" width="60.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.375" style="11" customWidth="1"/>
+    <col min="4" max="4" width="11.375" style="10" customWidth="1"/>
     <col min="5" max="5" width="43.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="8.25" style="3" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
@@ -3489,33 +3446,33 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>294</v>
+      <c r="D1" s="9" t="s">
+        <v>289</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3525,13 +3482,13 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3541,16 +3498,16 @@
     </row>
     <row r="6" spans="1:6" ht="27">
       <c r="A6" s="5" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3560,16 +3517,16 @@
     </row>
     <row r="8" spans="1:6" ht="27">
       <c r="A8" s="5" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3579,16 +3536,16 @@
     </row>
     <row r="10" spans="1:6" ht="27">
       <c r="A10" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3598,16 +3555,16 @@
     </row>
     <row r="12" spans="1:6" ht="27">
       <c r="A12" s="5" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3617,16 +3574,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3636,16 +3593,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -3655,115 +3612,115 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="27">
       <c r="A28" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="27">
       <c r="A30" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="27">
       <c r="A32" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="54">
       <c r="A34" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="67.5">
       <c r="A36" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -3771,13 +3728,13 @@
     </row>
     <row r="38" spans="1:3" ht="54">
       <c r="A38" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -3785,13 +3742,13 @@
     </row>
     <row r="40" spans="1:3" ht="54">
       <c r="A40" s="5" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -3799,13 +3756,13 @@
     </row>
     <row r="42" spans="1:3" ht="27">
       <c r="A42" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -3813,160 +3770,160 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="40.5">
       <c r="A46" s="5" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="5" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="C54" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="54">
       <c r="A56" s="5" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>329</v>
+        <v>154</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="40.5">
       <c r="A60" s="5" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="40.5">
       <c r="A62" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="27">
       <c r="A64" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D64" s="11" t="s">
-        <v>241</v>
+        <v>163</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D66" s="11" t="s">
-        <v>241</v>
+        <v>165</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3976,41 +3933,41 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D72" s="11" t="s">
-        <v>241</v>
+        <v>179</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -4020,13 +3977,13 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -4036,49 +3993,49 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="94.5">
       <c r="A84" s="5" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -4104,83 +4061,83 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="5" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="5" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="5" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:4" s="3" customFormat="1" ht="43.5" customHeight="1">

--- a/internal_doc/05.测试设计/驱动测试/PHP 驱动/PHP驱动_接口分析.xlsx
+++ b/internal_doc/05.测试设计/驱动测试/PHP 驱动/PHP驱动_接口分析.xlsx
@@ -8,25 +8,116 @@
   </bookViews>
   <sheets>
     <sheet name="设计说明" sheetId="5" r:id="rId1"/>
-    <sheet name="SequoiaDB" sheetId="4" r:id="rId2"/>
-    <sheet name="SequoiaGroup &amp; Node" sheetId="8" r:id="rId3"/>
-    <sheet name="SequoiaCS &amp; Domain" sheetId="7" r:id="rId4"/>
-    <sheet name="SequoiaCL &amp; Cursor" sheetId="6" r:id="rId5"/>
-    <sheet name="dataType接口" sheetId="9" r:id="rId6"/>
+    <sheet name="测试设计" sheetId="10" r:id="rId2"/>
+    <sheet name="SequoiaDB" sheetId="4" r:id="rId3"/>
+    <sheet name="SequoiaGroup &amp; Node" sheetId="8" r:id="rId4"/>
+    <sheet name="SequoiaCS &amp; Domain" sheetId="7" r:id="rId5"/>
+    <sheet name="SequoiaCL &amp; Cursor" sheetId="6" r:id="rId6"/>
+    <sheet name="dataType接口" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5">dataType接口!$A$1:$E$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'SequoiaCL &amp; Cursor'!$A$1:$F$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'SequoiaCS &amp; Domain'!$A$1:$G$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SequoiaDB!$A$1:$G$108</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SequoiaGroup &amp; Node'!$A$1:$G$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6">dataType接口!$A$1:$F$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'SequoiaCL &amp; Cursor'!$A$1:$F$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'SequoiaCS &amp; Domain'!$A$1:$F$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">SequoiaDB!$A$1:$F$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'SequoiaGroup &amp; Node'!$A$1:$F$44</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="C12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+有</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>BUG</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>，参数没生效</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C36" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+有</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Bug</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="461">
   <si>
     <t>备注</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -39,10 +130,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>install (array|string $options=null)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>install</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -59,10 +146,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>connect (array|string $address="127.0.0.1:11810", string $userName="", string $password="", boolean $useSSL=false)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>connect</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -83,10 +166,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>snapshot (integer $type, array|string $condition=null, array|string $selector=null, array|string $orderBy=null, array|string $hint=null)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>snapshot</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -103,19 +182,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>list (integer $type, array|string $condition=null, array|string $selector=null, array|string $orderBy=null, array|string $hint=null)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>list</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>测试策略：
-按用户使用场景分析接口，分析完成后再对比接口列表分析哪些接口没有覆盖到，并确定接口优先级</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">listCS </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -289,10 +359,6 @@
   </si>
   <si>
     <t>分类</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>不推荐使用的接口？？？</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -756,9 +822,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>getNext ()</t>
-  </si>
-  <si>
     <t>游标</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -964,12 +1027,6 @@
   </si>
   <si>
     <t>Timestamp</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>接口优先级：
-1、常用接口  --高，需要尽可能覆盖，并详细测试
-2、不常用/不重要的接口  --低，简单覆盖</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1317,34 +1374,6 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>selectCS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> instead</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">use the function </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>listCS()</t>
     </r>
     <r>
@@ -1608,15 +1637,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>对应自动化用例</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>创建/查询/删除/启动/停止组编目组</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>对应自动化用例</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1707,12 +1728,769 @@
     <t>evalJs (string $code)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>参数校验</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>接口优先级：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1、常用接口  --高，需要尽可能覆盖，并详细测试（包括参数校验）
+2、不常用/不重要的接口  --低，简单覆盖</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>测试策略：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1、按用户使用场景分析接口，分析完成后再对比接口列表分析哪些接口没有覆盖到，并确定接口优先级
+2、非驱动本身异常都是引擎处理，所以每个特性考虑一个非驱动本身异常场景即可</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">$flags：
+While </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SDB_FLG_INSERT_CONTONDUP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is set, if some records hit index key duplicate error, database will skip them and go on inserting. However, while </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is set, database will stop inserting in that case, and return errno code.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>$flag:
+The query flag, default to be 0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>$numToReturn:
+Only return numToReturn records, return all if this parameter is -1.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据类型分别覆盖最大、最小有效边界，无效取值挑其中一种数据类型的无效边界覆盖即可</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数校验</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>connect (array|string $address="127.0.0.1:11810", string $userName="", string $password="", boolean $useSSL=false)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>snapshot (integer $type, array|string $condition=null, array|string $selector=null, array|string $orderBy=null, array|string $hint=null)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求分类（接口）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>特性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一级子特性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>二级子特性</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库操作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>元数据操作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证create/alter/list/dropDomain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>domain/cs/cl基本功能组合验证</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证create/list/dropCS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通cl</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证create/alter/list/dropCL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>水平分区表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>垂直分区表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本数据操作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>覆盖所有数据类型（包括记录类型边界值）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">插入/更新/查询/删除基本功能可组合验证，重点验证数组类型；考虑是否带OID，并发插入的时候，会不会存在OID冲突
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>覆盖flag的不同取值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>导入数据文件验证字符编码问题</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证所有数据类型更新操作，覆盖更新符测试</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>delete</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除数据，可指定条件删除</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>query</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询条件组合验证</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>查询数据构造存在如下场景：字段值乱序（大小不一致）、字段无序、存在大记录、数据量较大</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cursor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用/关闭游标功能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引管理</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Index</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建/查询/删除索引</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>IdIndex</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lob</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入lob</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入lob（验证lob大小边界）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入/查询/删除基本功能组合验证</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据压缩</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>指定snappy/lzw类型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建CL指定压缩类型，覆盖数据操作基本功能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚集符组合验证</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>split</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>hash分区表和range分区表切分功能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>结合创建CL、插入数据等功能验证</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>splitAsync</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>权限管理</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建/删除用户，创建用户后执行基本数据操作</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>create/list/removeProcedure</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>验证备份恢复基本功能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SQL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群管理</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>分区组</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>编目分区组</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建/启动/停止/查询/删除分区组/选举</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>组管理和节点管理组合验证</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据分区组</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点管理</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据节点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建/启动/停止/查询/挂载/去挂载/删除节点</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动端并发操作（并发大量读写请求）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>内存泄露</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用工具验证</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常场景</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作过程中数据节点异常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数异常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb端返回消息体结构非法</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>文档实例验证</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>分别验证信息中心文档和sample中实例</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>list (integer $type, array|string $condition=null, array|string $selector=null, array|string $orderBy=null, array|string $hint=null)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PHP测试版本：信息中心推荐的版本</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PHP驱动端</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PHP版本测试</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）$taskID传参类型覆盖：array、integer、SequoiaInt64</t>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）只覆盖必填参数
+3）$rule/$condition/$hint传参类型覆盖：array、string</t>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）只覆盖必填参数
+3）$options传参类型覆盖：array、string</t>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）只覆盖必填参数
+3）$condition/$endCondition传参类型覆盖：array、string，且取值覆盖partition边界2^3、2^20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）$options传参类型覆盖：array、string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）只覆盖必填参数
+3）$condition/$selector/$orderBy/$hint传参类型覆盖：array、string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）只覆盖必填参数
+3）$options传参类型覆盖：array、string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）只覆盖必填参数
+3）$condition/$selector/$orderBy传参类型覆盖：array、string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）只覆盖必填参数
+3）$options传参类型覆盖：array、string
+4）$name字符长度：127B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）$options传参类型覆盖：array、string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>参数校验：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+挑重要接口重要参数取典型值覆盖（可以在同一个接口测试用例里面交叉覆盖）
+参数传参时重点针对数组测试</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）$args传参类型覆盖：$offset、SequoiaINT64</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）$sessionID传参类型覆盖：integer、SequoiaInt64</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>install (array|string $options=null)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）只覆盖必填参数
+3）$address传参类型覆盖：array、string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）只覆盖必填参数
+3）$condition/$selector/$orderBy/$hint传参类型覆盖：array、string
+4）$type覆盖一种取值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）$condition传参类型覆盖：array、string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）只覆盖必填参数
+3）$options/$condition/$selector/$orderBy/$hint传参类型覆盖：array、string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）只覆盖必填参数
+3）$configure传参类型覆盖：array、string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）覆盖status所有取值：覆盖一种取值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）$taskID传参类型覆盖：array、integer、SequoiaInt64</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）$record传参类型覆盖：array、string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）$records传参类型覆盖：array、string
+2）$flags取值覆盖：SDB_FLG_INSERT_CONTONDUP、0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）只覆盖必填参数
+3）$condition/$hint传参类型覆盖：array、string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）只覆盖必填参数
+3）$rule/$selector/$orderBy/$condition/$hint传参类型覆盖：array、string
+4）$numToReturn覆盖：
+   1）返回记录 &lt; 符合匹配条件的记录
+   2）返回记录 &gt; 符合匹配条件的记录
+   3）-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）只覆盖必填参数
+3）$selector/$orderBy/$condition/$hint传参类型覆盖：array、string
+4）$numToReturn覆盖：
+   1）返回记录 &lt; 符合匹配条件的记录
+   2）返回记录 &gt; 符合匹配条件的记录
+   3）-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）$aggrObj传参类型覆盖：array、string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）$args传参类型覆盖：integer、SequoiaINT64</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）只覆盖必填参数
+3）$options/$selector/$orderBy/$condition/$hint传参类型覆盖：array、string
+4）$numToReturn覆盖：
+   1）返回记录 &lt; 符合匹配条件的记录
+   2）返回记录 &gt; 符合匹配条件的记录
+   3）-1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）只覆盖必填参数
+3）$indexDef传参类型覆盖：array、string
+4）$indexName字符长度：1023B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）$indexName传值为空/非空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）$args传参类型覆盖：array、string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）$percent传参类型覆盖：integer、double，并覆盖小数和整数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）$percent传参类型覆盖：integer、double</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）覆盖所有参数
+2）只覆盖必填参数
+3）$condition/$endCondition传参类型覆盖：array、string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>getNodeName</t>
+  </si>
+  <si>
+    <t>deleteIndex</t>
+  </si>
+  <si>
+    <t>getCollectionName</t>
+  </si>
+  <si>
+    <t>dropCollection</t>
+  </si>
+  <si>
+    <t>selectCollection</t>
+  </si>
+  <si>
+    <t>getNext</t>
+  </si>
+  <si>
+    <t>dropCollectionSpace</t>
+  </si>
+  <si>
+    <t>getList</t>
+  </si>
+  <si>
+    <t>getSnapshot</t>
+  </si>
+  <si>
+    <t>listCollections</t>
+  </si>
+  <si>
+    <t>listCSs</t>
+  </si>
+  <si>
+    <t>listDomains</t>
+  </si>
+  <si>
+    <t>selectCS</t>
+  </si>
+  <si>
+    <t>selectGroup</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>不推荐使用的接口</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>列表如下（14个），只测试接口通道，传参时覆盖所有参数：</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>getNext ()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">use the function </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">selectCS( string $name, array|string $options = NULL ) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>instead</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PHP驱动端与sequoiadb端连接异常</t>
+  </si>
+  <si>
+    <t>PHP驱动端和sequoiadb网络异常</t>
+  </si>
+  <si>
+    <t>PHP驱动端传入参数不合法（如null）</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1768,8 +2546,45 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1784,6 +2599,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1803,7 +2624,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1838,6 +2659,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2140,28 +2970,511 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="59.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="40.5">
-      <c r="A1" s="1" t="s">
-        <v>234</v>
+      <c r="A1" s="11" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:1" ht="40.5">
-      <c r="A3" s="1" t="s">
-        <v>21</v>
-      </c>
+    <row r="3" spans="1:1" ht="67.5">
+      <c r="A3" s="11" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="54">
+      <c r="A5" s="11" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1"/>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="7" t="s">
-        <v>66</v>
+        <v>403</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="7"/>
+    </row>
+    <row r="10" spans="1:1" ht="27">
+      <c r="A10" s="11" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>441</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F40"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="2" width="13.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="45" style="1" customWidth="1"/>
+    <col min="6" max="6" width="58.375" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="27">
+      <c r="A1" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="1" customFormat="1">
+      <c r="A2" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="1" customFormat="1">
+      <c r="C3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="1" customFormat="1">
+      <c r="C4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="1" customFormat="1">
+      <c r="D5" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="1" customFormat="1">
+      <c r="D6" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="1" customFormat="1" ht="40.5">
+      <c r="B7" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="1" customFormat="1">
+      <c r="D8" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="1" customFormat="1">
+      <c r="C9" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="1" customFormat="1">
+      <c r="D10" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="1" customFormat="1">
+      <c r="C11" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="1" customFormat="1">
+      <c r="D12" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="1" customFormat="1" ht="27">
+      <c r="C13" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="1" customFormat="1">
+      <c r="D14" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="1" customFormat="1">
+      <c r="C15" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="1" customFormat="1">
+      <c r="D16" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="1" customFormat="1">
+      <c r="C17" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="1" customFormat="1">
+      <c r="D18" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="1" customFormat="1">
+      <c r="D19" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="1" customFormat="1">
+      <c r="C20" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="1" customFormat="1">
+      <c r="C21" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="1" customFormat="1">
+      <c r="B22" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="1" customFormat="1">
+      <c r="C23" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" s="1" customFormat="1">
+      <c r="B24" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" s="1" customFormat="1">
+      <c r="B25" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" s="1" customFormat="1">
+      <c r="B26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" s="1" customFormat="1">
+      <c r="B27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" s="1" customFormat="1">
+      <c r="B28" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" s="1" customFormat="1">
+      <c r="A29" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" s="1" customFormat="1">
+      <c r="C30" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" s="1" customFormat="1">
+      <c r="B31" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" s="1" customFormat="1">
+      <c r="A32" s="14" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" s="1" customFormat="1">
+      <c r="B33" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" s="1" customFormat="1">
+      <c r="B34" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" s="1" customFormat="1" ht="40.5">
+      <c r="B35" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" s="1" customFormat="1">
+      <c r="E36" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" s="1" customFormat="1">
+      <c r="C37" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" s="1" customFormat="1">
+      <c r="E38" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" s="1" customFormat="1">
+      <c r="B39" s="13" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" s="1" customFormat="1">
+      <c r="A40" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -2170,1037 +3483,781 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="14.5" style="5" customWidth="1"/>
-    <col min="2" max="2" width="21.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="19.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="60.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="41.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.25" style="3" customWidth="1"/>
-    <col min="7" max="7" width="26" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="46.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="41.125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>289</v>
+        <v>327</v>
       </c>
       <c r="E1" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="27">
+    </row>
+    <row r="2" spans="1:6" ht="27">
       <c r="A2" s="5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:6">
       <c r="B3" s="12"/>
     </row>
-    <row r="4" spans="1:7" ht="27">
+    <row r="4" spans="1:6" ht="27">
       <c r="A4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="40.5">
+      <c r="A8" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="70.5" customHeight="1">
+      <c r="A14" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="3" customFormat="1" ht="59.25" customHeight="1">
+      <c r="A18" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="54">
+      <c r="A20" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="40.5">
+      <c r="A22" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="40.5">
+      <c r="A24" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="54">
+      <c r="A30" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="54">
+      <c r="A36" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="B37" s="4"/>
+    </row>
+    <row r="38" spans="1:4" ht="40.5">
+      <c r="A38" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="B39" s="4"/>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="B41" s="4"/>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="B43" s="4"/>
+    </row>
+    <row r="44" spans="1:4" ht="54">
+      <c r="A44" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="40.5">
+      <c r="A52" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="5" t="s">
+      <c r="C62" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="54">
+      <c r="A64" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="67.5">
+      <c r="A80" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="54">
+      <c r="A84" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="27">
+      <c r="A86" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="27">
+      <c r="A88" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="27">
-      <c r="A8" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="42.75" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" s="3" customFormat="1" ht="43.5" customHeight="1">
-      <c r="A18" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="40.5">
-      <c r="A20" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="27">
-      <c r="A22" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="40.5">
-      <c r="A30" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="40.5">
-      <c r="A36" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="B37" s="4"/>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="B39" s="4"/>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="B41" s="4"/>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="B43" s="4"/>
-    </row>
-    <row r="44" spans="1:3" ht="40.5">
-      <c r="A44" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="27">
-      <c r="A52" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="40.5">
-      <c r="A64" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" ht="40.5">
-      <c r="A80" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="40.5">
-      <c r="A84" s="5" t="s">
+      <c r="C88" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="27">
+      <c r="A92" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="27">
+      <c r="A94" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E94" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="27">
+      <c r="A96" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="27">
-      <c r="A88" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="B88" s="1" t="s">
+      <c r="C96" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B90" s="1" t="s">
+      <c r="E96" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="40.5">
+      <c r="A98" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C98" s="1" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B92" s="1" t="s">
+      <c r="E98" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="27">
+      <c r="A100" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C100" s="1" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" ht="27" hidden="1">
-      <c r="A94" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B94" s="1" t="s">
+      <c r="E100" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" ht="27">
+      <c r="A102" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C102" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="27" hidden="1">
-      <c r="A96" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B96" s="1" t="s">
+      <c r="E102" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" ht="27">
+      <c r="A104" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C104" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D96" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="27" hidden="1">
-      <c r="A98" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B98" s="1" t="s">
+      <c r="E104" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="27">
+      <c r="A106" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C106" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" ht="27" hidden="1">
-      <c r="A100" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B100" s="1" t="s">
+      <c r="E106" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" ht="27">
+      <c r="A108" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C108" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="D100" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="27" hidden="1">
-      <c r="A102" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" ht="27" hidden="1">
-      <c r="A104" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="27" hidden="1">
-      <c r="A106" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="27" hidden="1">
-      <c r="A108" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>298</v>
+      <c r="E108" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G108">
+  <autoFilter ref="A1:F108">
     <filterColumn colId="0"/>
-    <filterColumn colId="3">
-      <filters blank="1"/>
-    </filterColumn>
+    <filterColumn colId="3"/>
+    <filterColumn colId="4"/>
   </autoFilter>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G44"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="10" style="5" customWidth="1"/>
-    <col min="2" max="2" width="16" style="1" customWidth="1"/>
-    <col min="3" max="3" width="55.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="10" customWidth="1"/>
-    <col min="5" max="5" width="41.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.25" style="3" customWidth="1"/>
-    <col min="7" max="7" width="41.125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="27">
-      <c r="A2" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="27">
-      <c r="A22" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="27">
-      <c r="A24" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="27">
-      <c r="A26" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="27">
-      <c r="A28" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G44"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3209,837 +4266,567 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="14.625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="21.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="60.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" customWidth="1"/>
-    <col min="5" max="5" width="41.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.25" style="3" customWidth="1"/>
-    <col min="7" max="7" width="41.125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="10" style="5" customWidth="1"/>
+    <col min="2" max="2" width="16" style="1" customWidth="1"/>
+    <col min="3" max="3" width="53" style="1" customWidth="1"/>
+    <col min="4" max="4" width="43.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" style="10" customWidth="1"/>
+    <col min="6" max="6" width="32.625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>305</v>
+        <v>89</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="E1" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+    </row>
+    <row r="2" spans="1:6" ht="27">
       <c r="A2" s="5" t="s">
-        <v>59</v>
+        <v>258</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>114</v>
+        <v>180</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="27">
+        <v>179</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>60</v>
+        <v>258</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>60</v>
+        <v>258</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>60</v>
+        <v>258</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>33</v>
+        <v>182</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="40.5">
       <c r="A10" s="5" t="s">
-        <v>60</v>
+        <v>258</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>183</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>60</v>
+        <v>258</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D12" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="40.5">
+      <c r="A22" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="40.5">
+      <c r="A24" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="40.5">
+      <c r="A26" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="40.5">
+      <c r="A28" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="B15" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="40.5">
-      <c r="A18" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="40.5">
-      <c r="A20" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="40.5">
-      <c r="A22" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="B29" s="4"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="B30" s="4"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="B31" s="4"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="B32" s="4"/>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="4"/>
-    </row>
-    <row r="34" spans="2:2">
-      <c r="B34" s="4"/>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" s="4"/>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" s="4"/>
-    </row>
-    <row r="37" spans="2:2">
-      <c r="B37" s="4"/>
+    </row>
+    <row r="44" spans="1:6" ht="27">
+      <c r="A44" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>282</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G37"/>
+  <autoFilter ref="A1:F44">
+    <filterColumn colId="3"/>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="5" customWidth="1"/>
-    <col min="2" max="2" width="21.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="60.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.375" style="10" customWidth="1"/>
-    <col min="5" max="5" width="43.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.25" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="19.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="57.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="43.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" customWidth="1"/>
+    <col min="6" max="6" width="38.5" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>289</v>
+        <v>13</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>320</v>
       </c>
       <c r="E1" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>0</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="5" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="54">
       <c r="A4" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>98</v>
+        <v>162</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="27">
+        <v>161</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="40.5">
       <c r="A6" s="5" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="B7" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="27">
+        <v>163</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="27">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>106</v>
+        <v>167</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="27">
       <c r="A12" s="5" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>106</v>
+        <v>169</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="B13" s="1" t="s">
-        <v>1</v>
+        <v>168</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>270</v>
+        <v>170</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>91</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="54">
       <c r="A18" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>305</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="54">
       <c r="A20" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>25</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="54">
       <c r="A22" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="27">
-      <c r="A28" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="27">
-      <c r="A30" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="27">
-      <c r="A32" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="54">
-      <c r="A34" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="67.5">
-      <c r="A36" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
+        <v>39</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="B29" s="4"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="B30" s="4"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="B31" s="4"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="B32" s="4"/>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="4"/>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="4"/>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="4"/>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="4"/>
+    </row>
+    <row r="37" spans="2:2">
       <c r="B37" s="4"/>
     </row>
-    <row r="38" spans="1:3" ht="54">
-      <c r="A38" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="B39" s="4"/>
-    </row>
-    <row r="40" spans="1:3" ht="54">
-      <c r="A40" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="B41" s="4"/>
-    </row>
-    <row r="42" spans="1:3" ht="27">
-      <c r="A42" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="B43" s="4"/>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="40.5">
-      <c r="A46" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="54">
-      <c r="A56" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="40.5">
-      <c r="A60" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="40.5">
-      <c r="A62" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="27">
-      <c r="A64" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D64" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="C69" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D72" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="B75" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="B77" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="94.5">
-      <c r="A84" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>288</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F84"/>
+  <autoFilter ref="A1:F37">
+    <filterColumn colId="3"/>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4048,106 +4835,814 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:F84"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="9.625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="15.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="58.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="45.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.375" style="10" customWidth="1"/>
+    <col min="6" max="6" width="40.25" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="40.5">
+      <c r="A6" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="54">
+      <c r="A8" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="27">
+      <c r="A10" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="54">
+      <c r="A12" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="27">
+      <c r="A20" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="108">
+      <c r="A26" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="40.5">
+      <c r="A28" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="54">
+      <c r="A30" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="54">
+      <c r="A32" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="54">
+      <c r="A34" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="108">
+      <c r="A36" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="B37" s="4"/>
+    </row>
+    <row r="38" spans="1:6" ht="108">
+      <c r="A38" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="4"/>
+    </row>
+    <row r="40" spans="1:6" ht="121.5">
+      <c r="A40" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="4"/>
+    </row>
+    <row r="42" spans="1:6" ht="40.5">
+      <c r="A42" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="B43" s="4"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="54">
+      <c r="A46" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="54">
+      <c r="A56" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="54">
+      <c r="A60" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="54">
+      <c r="A62" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="27">
+      <c r="A64" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E64" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E66" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="C69" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="E72" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="94.5">
+      <c r="A84" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F84">
+    <filterColumn colId="3"/>
+  </autoFilter>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16.625" style="5" customWidth="1"/>
     <col min="2" max="2" width="46.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13" style="1" customWidth="1"/>
-    <col min="4" max="4" width="41.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.25" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="3" max="3" width="39.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="1" customWidth="1"/>
+    <col min="5" max="5" width="41.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.25" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="8" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="27">
       <c r="A2" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="5" t="s">
+      <c r="B10" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" s="3" customFormat="1" ht="43.5" customHeight="1">
+    </row>
+    <row r="18" spans="1:5" s="3" customFormat="1" ht="43.5" customHeight="1">
       <c r="A18" s="5"/>
       <c r="B18" s="1"/>
-      <c r="D18" s="2"/>
+      <c r="C18" s="1"/>
+      <c r="E18" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E44">
+  <autoFilter ref="A1:F44">
     <filterColumn colId="2"/>
+    <filterColumn colId="3"/>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/internal_doc/05.测试设计/驱动测试/PHP 驱动/PHP驱动_接口分析.xlsx
+++ b/internal_doc/05.测试设计/驱动测试/PHP 驱动/PHP驱动_接口分析.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="设计说明" sheetId="5" r:id="rId1"/>
@@ -3100,7 +3100,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="27">
+    <row r="1" spans="1:6" ht="27">
       <c r="A1" s="1" t="s">
         <v>330</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="1" customFormat="1">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>335</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="1" customFormat="1">
+    <row r="3" spans="1:6">
       <c r="C3" s="1" t="s">
         <v>54</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="1" customFormat="1">
+    <row r="4" spans="1:6">
       <c r="C4" s="1" t="s">
         <v>55</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="1" customFormat="1">
+    <row r="5" spans="1:6">
       <c r="D5" s="1" t="s">
         <v>343</v>
       </c>
@@ -3164,7 +3164,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="1" customFormat="1">
+    <row r="6" spans="1:6">
       <c r="D6" s="1" t="s">
         <v>344</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="1" customFormat="1" ht="40.5">
+    <row r="7" spans="1:6" ht="40.5">
       <c r="B7" s="1" t="s">
         <v>345</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="1" customFormat="1">
+    <row r="8" spans="1:6">
       <c r="D8" s="1" t="s">
         <v>116</v>
       </c>
@@ -3200,7 +3200,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="1" customFormat="1">
+    <row r="9" spans="1:6">
       <c r="C9" s="1" t="s">
         <v>351</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="1" customFormat="1">
+    <row r="10" spans="1:6">
       <c r="D10" s="1" t="s">
         <v>120</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="1" customFormat="1">
+    <row r="11" spans="1:6">
       <c r="C11" s="1" t="s">
         <v>353</v>
       </c>
@@ -3230,12 +3230,12 @@
         <v>355</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="1" customFormat="1">
+    <row r="12" spans="1:6">
       <c r="D12" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="1" customFormat="1" ht="27">
+    <row r="13" spans="1:6" ht="27">
       <c r="C13" s="1" t="s">
         <v>356</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="1" customFormat="1">
+    <row r="14" spans="1:6">
       <c r="D14" s="1" t="s">
         <v>360</v>
       </c>
@@ -3257,7 +3257,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="1" customFormat="1">
+    <row r="15" spans="1:6">
       <c r="C15" s="1" t="s">
         <v>362</v>
       </c>
@@ -3268,7 +3268,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="16" spans="1:6" s="1" customFormat="1">
+    <row r="16" spans="1:6">
       <c r="D16" s="1" t="s">
         <v>365</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="1" customFormat="1">
+    <row r="17" spans="1:6">
       <c r="C17" s="1" t="s">
         <v>366</v>
       </c>
@@ -3290,17 +3290,17 @@
         <v>369</v>
       </c>
     </row>
-    <row r="18" spans="1:6" s="1" customFormat="1">
+    <row r="18" spans="1:6">
       <c r="D18" s="1" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="1" customFormat="1">
+    <row r="19" spans="1:6">
       <c r="D19" s="1" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="20" spans="1:6" s="1" customFormat="1">
+    <row r="20" spans="1:6">
       <c r="C20" s="1" t="s">
         <v>370</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="21" spans="1:6" s="1" customFormat="1">
+    <row r="21" spans="1:6">
       <c r="C21" s="1" t="s">
         <v>143</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="22" spans="1:6" s="1" customFormat="1">
+    <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
         <v>374</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="23" spans="1:6" s="1" customFormat="1">
+    <row r="23" spans="1:6">
       <c r="C23" s="1" t="s">
         <v>377</v>
       </c>
@@ -3344,12 +3344,12 @@
         <v>376</v>
       </c>
     </row>
-    <row r="24" spans="1:6" s="1" customFormat="1">
+    <row r="24" spans="1:6">
       <c r="B24" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:6" s="1" customFormat="1">
+    <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
         <v>378</v>
       </c>
@@ -3357,7 +3357,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="26" spans="1:6" s="1" customFormat="1">
+    <row r="26" spans="1:6">
       <c r="B26" s="1" t="s">
         <v>63</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="27" spans="1:6" s="1" customFormat="1">
+    <row r="27" spans="1:6">
       <c r="B27" s="1" t="s">
         <v>65</v>
       </c>
@@ -3373,12 +3373,12 @@
         <v>381</v>
       </c>
     </row>
-    <row r="28" spans="1:6" s="1" customFormat="1">
+    <row r="28" spans="1:6">
       <c r="B28" s="1" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="29" spans="1:6" s="1" customFormat="1">
+    <row r="29" spans="1:6">
       <c r="A29" s="1" t="s">
         <v>383</v>
       </c>
@@ -3395,7 +3395,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="30" spans="1:6" s="1" customFormat="1">
+    <row r="30" spans="1:6">
       <c r="C30" s="1" t="s">
         <v>388</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="31" spans="1:6" s="1" customFormat="1">
+    <row r="31" spans="1:6">
       <c r="B31" s="1" t="s">
         <v>389</v>
       </c>
@@ -3414,12 +3414,12 @@
         <v>391</v>
       </c>
     </row>
-    <row r="32" spans="1:6" s="1" customFormat="1">
+    <row r="32" spans="1:6">
       <c r="A32" s="14" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="33" spans="1:5" s="1" customFormat="1">
+    <row r="33" spans="1:5">
       <c r="B33" s="1" t="s">
         <v>392</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="34" spans="1:5" s="1" customFormat="1">
+    <row r="34" spans="1:5">
       <c r="B34" s="1" t="s">
         <v>394</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="35" spans="1:5" s="1" customFormat="1" ht="40.5">
+    <row r="35" spans="1:5" ht="40.5">
       <c r="B35" s="1" t="s">
         <v>396</v>
       </c>
@@ -3446,12 +3446,12 @@
         <v>459</v>
       </c>
     </row>
-    <row r="36" spans="1:5" s="1" customFormat="1">
+    <row r="36" spans="1:5">
       <c r="E36" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="37" spans="1:5" s="1" customFormat="1">
+    <row r="37" spans="1:5">
       <c r="C37" s="1" t="s">
         <v>398</v>
       </c>
@@ -3459,17 +3459,17 @@
         <v>460</v>
       </c>
     </row>
-    <row r="38" spans="1:5" s="1" customFormat="1">
+    <row r="38" spans="1:5">
       <c r="E38" s="1" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="39" spans="1:5" s="1" customFormat="1">
+    <row r="39" spans="1:5">
       <c r="B39" s="13" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="40" spans="1:5" s="1" customFormat="1">
+    <row r="40" spans="1:5">
       <c r="A40" s="14" t="s">
         <v>400</v>
       </c>

--- a/internal_doc/05.测试设计/驱动测试/PHP 驱动/PHP驱动_接口分析.xlsx
+++ b/internal_doc/05.测试设计/驱动测试/PHP 驱动/PHP驱动_接口分析.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="设计说明" sheetId="5" r:id="rId1"/>
@@ -73,7 +73,45 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>，参数没生效</t>
+          <t>，参数没生效，跟</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>getStatus</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>接口属于同一类问题。开发有提单，未修改</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">  ----</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>谭钊波</t>
         </r>
       </text>
     </comment>
@@ -110,6 +148,36 @@
           </rPr>
           <t>Bug</t>
         </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">，获取不到节点状态。开发已提单，未修改
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>----</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>谭钊波</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -947,9 +1015,6 @@
   </si>
   <si>
     <t>getServiceName ()</t>
-  </si>
-  <si>
-    <t>getStatus ()</t>
   </si>
   <si>
     <t>getHostName</t>
@@ -2287,10 +2352,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1）覆盖status所有取值：覆盖一种取值</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1）$taskID传参类型覆盖：array、integer、SequoiaInt64</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2484,6 +2545,14 @@
   </si>
   <si>
     <t>PHP驱动端传入参数不合法（如null）</t>
+  </si>
+  <si>
+    <t>1）status取值：覆盖一种取值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>getStatus ()</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2978,7 +3047,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="40.5">
       <c r="A1" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -2986,12 +3055,12 @@
     </row>
     <row r="3" spans="1:1" ht="67.5">
       <c r="A3" s="11" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="54">
       <c r="A5" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -2999,7 +3068,7 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -3007,77 +3076,77 @@
     </row>
     <row r="10" spans="1:1" ht="27">
       <c r="A10" s="11" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -3102,19 +3171,19 @@
   <sheetData>
     <row r="1" spans="1:6" ht="27">
       <c r="A1" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>334</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
@@ -3122,19 +3191,19 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3142,7 +3211,7 @@
         <v>54</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3150,43 +3219,43 @@
         <v>55</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="D5" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="D6" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="40.5">
       <c r="B7" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>346</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>114</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3194,15 +3263,15 @@
         <v>116</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="C9" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>122</v>
@@ -3216,18 +3285,18 @@
         <v>120</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="C11" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3237,57 +3306,57 @@
     </row>
     <row r="13" spans="1:6" ht="27">
       <c r="C13" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="D14" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="C15" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="D16" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="C17" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -3302,13 +3371,13 @@
     </row>
     <row r="20" spans="1:6">
       <c r="C20" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -3316,32 +3385,32 @@
         <v>143</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="C23" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -3351,10 +3420,10 @@
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -3362,7 +3431,7 @@
         <v>63</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -3370,111 +3439,111 @@
         <v>65</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="C30" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="B31" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="E31" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="B33" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="B34" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="40.5">
       <c r="B35" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="E36" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="C37" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="E38" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="B39" s="13" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -3502,16 +3571,16 @@
         <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>0</v>
@@ -3522,7 +3591,7 @@
         <v>61</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
@@ -3539,15 +3608,15 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -3558,21 +3627,21 @@
     </row>
     <row r="8" spans="1:6" ht="40.5">
       <c r="A8" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
@@ -3583,7 +3652,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>11</v>
@@ -3594,24 +3663,24 @@
     </row>
     <row r="14" spans="1:6" ht="70.5" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>15</v>
@@ -3620,21 +3689,21 @@
         <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="3" customFormat="1" ht="59.25" customHeight="1">
       <c r="A18" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>88</v>
@@ -3648,10 +3717,10 @@
         <v>17</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="40.5">
@@ -3662,10 +3731,10 @@
         <v>18</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>87</v>
@@ -3682,7 +3751,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -3718,7 +3787,7 @@
         <v>25</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -3734,7 +3803,7 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>30</v>
@@ -3754,7 +3823,7 @@
         <v>31</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -3771,7 +3840,7 @@
         <v>33</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3816,7 +3885,7 @@
         <v>39</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3835,7 +3904,7 @@
         <v>57</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>43</v>
@@ -3846,7 +3915,7 @@
         <v>57</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>45</v>
@@ -3857,16 +3926,16 @@
         <v>57</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -3915,7 +3984,7 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>67</v>
@@ -3938,7 +4007,7 @@
         <v>68</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3965,13 +4034,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -4018,7 +4087,7 @@
         <v>80</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="67.5">
@@ -4032,7 +4101,7 @@
         <v>82</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -4048,208 +4117,208 @@
     </row>
     <row r="84" spans="1:6" ht="54">
       <c r="A84" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="27">
       <c r="A86" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="27">
       <c r="A88" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="27">
       <c r="A92" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="27">
       <c r="A94" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E94" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="E94" s="14" t="s">
-        <v>228</v>
-      </c>
       <c r="F94" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="27">
       <c r="A96" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E96" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E96" s="14" t="s">
-        <v>228</v>
-      </c>
       <c r="F96" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="40.5">
       <c r="A98" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E98" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="27">
       <c r="A100" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="27">
       <c r="A102" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E102" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="27">
       <c r="A104" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E104" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="27">
       <c r="A106" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E106" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="27">
       <c r="A108" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E108" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -4289,10 +4358,10 @@
         <v>13</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>0</v>
@@ -4300,7 +4369,7 @@
     </row>
     <row r="2" spans="1:6" ht="27">
       <c r="A2" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>180</v>
@@ -4309,7 +4378,7 @@
         <v>179</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4319,7 +4388,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>108</v>
@@ -4335,7 +4404,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>181</v>
@@ -4346,7 +4415,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>182</v>
@@ -4357,7 +4426,7 @@
     </row>
     <row r="10" spans="1:6" ht="40.5">
       <c r="A10" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>184</v>
@@ -4366,15 +4435,15 @@
         <v>183</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>186</v>
@@ -4383,15 +4452,15 @@
         <v>185</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>425</v>
+        <v>459</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>188</v>
@@ -4402,7 +4471,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>190</v>
@@ -4413,7 +4482,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>192</v>
@@ -4424,7 +4493,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>194</v>
@@ -4435,7 +4504,7 @@
     </row>
     <row r="22" spans="1:4" ht="40.5">
       <c r="A22" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>196</v>
@@ -4444,12 +4513,12 @@
         <v>195</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="40.5">
       <c r="A24" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>198</v>
@@ -4458,12 +4527,12 @@
         <v>197</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="40.5">
       <c r="A26" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>200</v>
@@ -4472,12 +4541,12 @@
         <v>199</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="40.5">
       <c r="A28" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>202</v>
@@ -4486,7 +4555,7 @@
         <v>201</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -4505,7 +4574,7 @@
         <v>203</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>204</v>
@@ -4516,7 +4585,7 @@
         <v>203</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>205</v>
@@ -4527,10 +4596,10 @@
         <v>203</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>206</v>
+        <v>460</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -4541,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -4571,16 +4640,16 @@
         <v>203</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -4613,16 +4682,16 @@
         <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>0</v>
@@ -4650,10 +4719,10 @@
         <v>161</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="40.5">
@@ -4667,7 +4736,7 @@
         <v>163</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4706,7 +4775,7 @@
         <v>172</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4723,7 +4792,7 @@
         <v>172</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4742,7 +4811,7 @@
         <v>91</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="54">
@@ -4753,13 +4822,13 @@
         <v>17</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="54">
@@ -4773,10 +4842,10 @@
         <v>25</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="54">
@@ -4790,10 +4859,10 @@
         <v>39</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -4852,16 +4921,16 @@
         <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>0</v>
@@ -4875,7 +4944,7 @@
         <v>90</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4894,7 +4963,7 @@
         <v>91</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4913,7 +4982,7 @@
         <v>93</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>97</v>
@@ -4935,7 +5004,7 @@
         <v>95</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>98</v>
@@ -4957,7 +5026,7 @@
         <v>99</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>101</v>
@@ -4976,10 +5045,10 @@
         <v>100</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>102</v>
@@ -5001,7 +5070,7 @@
         <v>103</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -5020,7 +5089,7 @@
         <v>105</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5039,7 +5108,7 @@
         <v>107</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="27">
@@ -5053,7 +5122,7 @@
         <v>109</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -5078,7 +5147,7 @@
         <v>113</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="108">
@@ -5092,10 +5161,10 @@
         <v>115</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="40.5">
@@ -5109,7 +5178,7 @@
         <v>117</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="54">
@@ -5123,7 +5192,7 @@
         <v>119</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="54">
@@ -5137,7 +5206,7 @@
         <v>121</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="54">
@@ -5151,10 +5220,10 @@
         <v>123</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="108">
@@ -5168,7 +5237,7 @@
         <v>125</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -5185,10 +5254,10 @@
         <v>127</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -5205,7 +5274,7 @@
         <v>130</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -5222,7 +5291,7 @@
         <v>132</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -5239,7 +5308,7 @@
         <v>134</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="54">
@@ -5253,7 +5322,7 @@
         <v>136</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -5278,7 +5347,7 @@
         <v>140</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -5292,7 +5361,7 @@
         <v>144</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -5317,7 +5386,7 @@
         <v>148</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -5342,7 +5411,7 @@
         <v>153</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="54">
@@ -5356,7 +5425,7 @@
         <v>155</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="27">
@@ -5370,10 +5439,10 @@
         <v>157</v>
       </c>
       <c r="E64" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -5387,10 +5456,10 @@
         <v>159</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -5401,7 +5470,7 @@
         <v>174</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -5417,7 +5486,7 @@
         <v>175</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5428,24 +5497,24 @@
         <v>176</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -5455,13 +5524,13 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -5471,55 +5540,55 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="94.5">
       <c r="A84" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -5551,13 +5620,13 @@
         <v>60</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>0</v>
@@ -5568,69 +5637,69 @@
     </row>
     <row r="2" spans="1:6" ht="27">
       <c r="A2" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="3" customFormat="1" ht="43.5" customHeight="1">
